--- a/artfynd/A 35202-2025 artfynd.xlsx
+++ b/artfynd/A 35202-2025 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>137370887</v>
       </c>
       <c r="B8" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35202-2025 artfynd.xlsx
+++ b/artfynd/A 35202-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370906</v>
       </c>
       <c r="B2" t="n">
-        <v>79597</v>
+        <v>79602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370899</v>
       </c>
       <c r="B3" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370892</v>
       </c>
       <c r="B4" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370896</v>
       </c>
       <c r="B5" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370905</v>
       </c>
       <c r="B6" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370894</v>
       </c>
       <c r="B7" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370887</v>
       </c>
       <c r="B8" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370891</v>
       </c>
       <c r="B9" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370886</v>
       </c>
       <c r="B10" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370889</v>
       </c>
       <c r="B11" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370904</v>
       </c>
       <c r="B12" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370898</v>
       </c>
       <c r="B13" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370902</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137370903</v>
       </c>
       <c r="B15" t="n">
-        <v>75463</v>
+        <v>75468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370895</v>
       </c>
       <c r="B16" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370900</v>
       </c>
       <c r="B17" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370885</v>
       </c>
       <c r="B18" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370897</v>
       </c>
       <c r="B19" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35202-2025 artfynd.xlsx
+++ b/artfynd/A 35202-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370906</v>
       </c>
       <c r="B2" t="n">
-        <v>79602</v>
+        <v>79613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370899</v>
       </c>
       <c r="B3" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370892</v>
       </c>
       <c r="B4" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370896</v>
       </c>
       <c r="B5" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370905</v>
       </c>
       <c r="B6" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370894</v>
       </c>
       <c r="B7" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370887</v>
       </c>
       <c r="B8" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370891</v>
       </c>
       <c r="B9" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370886</v>
       </c>
       <c r="B10" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370889</v>
       </c>
       <c r="B11" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370904</v>
       </c>
       <c r="B12" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370898</v>
       </c>
       <c r="B13" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370902</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137370903</v>
       </c>
       <c r="B15" t="n">
-        <v>75468</v>
+        <v>75479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370895</v>
       </c>
       <c r="B16" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370900</v>
       </c>
       <c r="B17" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370885</v>
       </c>
       <c r="B18" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370897</v>
       </c>
       <c r="B19" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35202-2025 artfynd.xlsx
+++ b/artfynd/A 35202-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370906</v>
       </c>
       <c r="B2" t="n">
-        <v>79613</v>
+        <v>79614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370899</v>
       </c>
       <c r="B3" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370892</v>
       </c>
       <c r="B4" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370896</v>
       </c>
       <c r="B5" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370905</v>
       </c>
       <c r="B6" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370894</v>
       </c>
       <c r="B7" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370887</v>
       </c>
       <c r="B8" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370891</v>
       </c>
       <c r="B9" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370886</v>
       </c>
       <c r="B10" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370889</v>
       </c>
       <c r="B11" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370904</v>
       </c>
       <c r="B12" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370898</v>
       </c>
       <c r="B13" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370902</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370895</v>
       </c>
       <c r="B16" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370900</v>
       </c>
       <c r="B17" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370885</v>
       </c>
       <c r="B18" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370897</v>
       </c>
       <c r="B19" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35202-2025 artfynd.xlsx
+++ b/artfynd/A 35202-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370906</v>
       </c>
       <c r="B2" t="n">
-        <v>79614</v>
+        <v>79616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370899</v>
       </c>
       <c r="B3" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370892</v>
       </c>
       <c r="B4" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370896</v>
       </c>
       <c r="B5" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370905</v>
       </c>
       <c r="B6" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370894</v>
       </c>
       <c r="B7" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370887</v>
       </c>
       <c r="B8" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370891</v>
       </c>
       <c r="B9" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370886</v>
       </c>
       <c r="B10" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370889</v>
       </c>
       <c r="B11" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370904</v>
       </c>
       <c r="B12" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370898</v>
       </c>
       <c r="B13" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370902</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370895</v>
       </c>
       <c r="B16" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370900</v>
       </c>
       <c r="B17" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370885</v>
       </c>
       <c r="B18" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370897</v>
       </c>
       <c r="B19" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35202-2025 artfynd.xlsx
+++ b/artfynd/A 35202-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370906</v>
       </c>
       <c r="B2" t="n">
-        <v>79616</v>
+        <v>79620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370899</v>
       </c>
       <c r="B3" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370892</v>
       </c>
       <c r="B4" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370896</v>
       </c>
       <c r="B5" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370905</v>
       </c>
       <c r="B6" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370894</v>
       </c>
       <c r="B7" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370887</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370891</v>
       </c>
       <c r="B9" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370886</v>
       </c>
       <c r="B10" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370889</v>
       </c>
       <c r="B11" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370904</v>
       </c>
       <c r="B12" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370898</v>
       </c>
       <c r="B13" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137370902</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137370903</v>
       </c>
       <c r="B15" t="n">
-        <v>75479</v>
+        <v>75483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137370895</v>
       </c>
       <c r="B16" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137370900</v>
       </c>
       <c r="B17" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137370885</v>
       </c>
       <c r="B18" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137370897</v>
       </c>
       <c r="B19" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
